--- a/FileExcel/EmployeeList_EN.xlsx
+++ b/FileExcel/EmployeeList_EN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Tue\MyProject\ManagerAttendance\FileExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3E2476-4F7A-495D-9461-257B18185696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56799C8E-56D4-469C-A151-D57DACB602CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30975" yWindow="5655" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
